--- a/data/odds/Ketkar Fantasy Football 2026 2026 Betting Odds.xlsx
+++ b/data/odds/Ketkar Fantasy Football 2026 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="56">
   <si>
     <t>Record</t>
   </si>
@@ -36,151 +36,154 @@
     <t>Austin Powers</t>
   </si>
   <si>
+    <t xml:space="preserve">Ashu’s Seahawks </t>
+  </si>
+  <si>
     <t>Walnut Rushers</t>
   </si>
   <si>
-    <t xml:space="preserve">Ashu’s Seahawks </t>
+    <t>Sharrell’s Peril</t>
   </si>
   <si>
     <t>FP Jets</t>
   </si>
   <si>
+    <t>Akshata's Angry Team</t>
+  </si>
+  <si>
     <t>Lox, Stocks and 2 Skattebooms!</t>
   </si>
   <si>
-    <t>Sharrell’s Peril</t>
-  </si>
-  <si>
-    <t>Akshata's Angry Team</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gotham City Gridiron Gang </t>
   </si>
   <si>
+    <t>3-1</t>
+  </si>
+  <si>
     <t>2-1</t>
   </si>
   <si>
-    <t>2-0</t>
+    <t>2-2</t>
   </si>
   <si>
     <t>1-2</t>
   </si>
   <si>
-    <t>0-3</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>99.7%</t>
-  </si>
-  <si>
-    <t>91.5%</t>
-  </si>
-  <si>
-    <t>84.5%</t>
-  </si>
-  <si>
-    <t>78.2%</t>
-  </si>
-  <si>
-    <t>33.9%</t>
-  </si>
-  <si>
-    <t>8.0%</t>
-  </si>
-  <si>
-    <t>3.5%</t>
-  </si>
-  <si>
-    <t>0.7%</t>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>99.9%</t>
+  </si>
+  <si>
+    <t>98.9%</t>
+  </si>
+  <si>
+    <t>72.1%</t>
+  </si>
+  <si>
+    <t>68.4%</t>
+  </si>
+  <si>
+    <t>47.9%</t>
+  </si>
+  <si>
+    <t>7.2%</t>
+  </si>
+  <si>
+    <t>3.0%</t>
+  </si>
+  <si>
+    <t>2.5%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-8991</t>
+  </si>
+  <si>
+    <t>-258</t>
+  </si>
+  <si>
+    <t>-216</t>
+  </si>
+  <si>
+    <t>+109</t>
+  </si>
+  <si>
+    <t>+1289</t>
+  </si>
+  <si>
+    <t>+3233</t>
+  </si>
+  <si>
+    <t>+3900</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>55.5%</t>
+  </si>
+  <si>
+    <t>39.8%</t>
+  </si>
+  <si>
+    <t>2.1%</t>
+  </si>
+  <si>
+    <t>1.8%</t>
+  </si>
+  <si>
+    <t>0.8%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-33233</t>
-  </si>
-  <si>
-    <t>-1076</t>
-  </si>
-  <si>
-    <t>-545</t>
-  </si>
-  <si>
-    <t>-359</t>
-  </si>
-  <si>
-    <t>+195</t>
-  </si>
-  <si>
-    <t>+1150</t>
-  </si>
-  <si>
-    <t>+2757</t>
-  </si>
-  <si>
-    <t>+14186</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>75.6%</t>
-  </si>
-  <si>
-    <t>12.0%</t>
-  </si>
-  <si>
-    <t>7.0%</t>
-  </si>
-  <si>
-    <t>4.9%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>-310</t>
-  </si>
-  <si>
-    <t>+733</t>
-  </si>
-  <si>
-    <t>+1329</t>
-  </si>
-  <si>
-    <t>+1941</t>
-  </si>
-  <si>
-    <t>+19900</t>
-  </si>
-  <si>
-    <t>44.9%</t>
-  </si>
-  <si>
-    <t>40.4%</t>
-  </si>
-  <si>
-    <t>11.6%</t>
-  </si>
-  <si>
-    <t>2.6%</t>
-  </si>
-  <si>
-    <t>+123</t>
-  </si>
-  <si>
-    <t>+148</t>
-  </si>
-  <si>
-    <t>+762</t>
-  </si>
-  <si>
-    <t>+3746</t>
+    <t>-125</t>
+  </si>
+  <si>
+    <t>+151</t>
+  </si>
+  <si>
+    <t>+4662</t>
+  </si>
+  <si>
+    <t>+5456</t>
+  </si>
+  <si>
+    <t>+12400</t>
+  </si>
+  <si>
+    <t>59.3%</t>
+  </si>
+  <si>
+    <t>17.8%</t>
+  </si>
+  <si>
+    <t>17.1%</t>
+  </si>
+  <si>
+    <t>5.5%</t>
+  </si>
+  <si>
+    <t>-146</t>
+  </si>
+  <si>
+    <t>+462</t>
+  </si>
+  <si>
+    <t>+485</t>
+  </si>
+  <si>
+    <t>+1718</t>
   </si>
 </sst>
 </file>
@@ -588,7 +591,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
@@ -602,7 +605,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
@@ -644,7 +647,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
@@ -672,7 +675,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
@@ -716,7 +719,7 @@
         <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -730,7 +733,7 @@
         <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -738,13 +741,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
         <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -752,13 +755,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -772,18 +775,18 @@
         <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
         <v>35</v>
@@ -791,13 +794,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
         <v>35</v>
@@ -805,13 +808,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
         <v>35</v>
@@ -819,13 +822,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
         <v>35</v>
@@ -860,13 +863,13 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -877,10 +880,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -888,13 +891,13 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -905,10 +908,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -919,15 +922,15 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -941,10 +944,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
@@ -955,13 +958,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
         <v>35</v>
@@ -969,13 +972,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
         <v>35</v>

--- a/data/odds/Ketkar Fantasy Football 2026 2026 Betting Odds.xlsx
+++ b/data/odds/Ketkar Fantasy Football 2026 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="57">
   <si>
     <t>Record</t>
   </si>
@@ -36,154 +36,157 @@
     <t>Austin Powers</t>
   </si>
   <si>
+    <t>Sharrell’s Peril</t>
+  </si>
+  <si>
+    <t>Walnut Rushers</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ashu’s Seahawks </t>
   </si>
   <si>
-    <t>Walnut Rushers</t>
-  </si>
-  <si>
-    <t>Sharrell’s Peril</t>
+    <t xml:space="preserve">Gotham City Gridiron Gang </t>
   </si>
   <si>
     <t>FP Jets</t>
   </si>
   <si>
+    <t>Lox, Stocks and 2 Skattebooms!</t>
+  </si>
+  <si>
     <t>Akshata's Angry Team</t>
   </si>
   <si>
-    <t>Lox, Stocks and 2 Skattebooms!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotham City Gridiron Gang </t>
+    <t>3-2</t>
   </si>
   <si>
     <t>3-1</t>
   </si>
   <si>
-    <t>2-1</t>
-  </si>
-  <si>
     <t>2-2</t>
   </si>
   <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-4</t>
-  </si>
-  <si>
-    <t>99.9%</t>
-  </si>
-  <si>
-    <t>98.9%</t>
-  </si>
-  <si>
-    <t>72.1%</t>
-  </si>
-  <si>
-    <t>68.4%</t>
-  </si>
-  <si>
-    <t>47.9%</t>
-  </si>
-  <si>
-    <t>7.2%</t>
-  </si>
-  <si>
-    <t>3.0%</t>
-  </si>
-  <si>
-    <t>2.5%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>-99900</t>
-  </si>
-  <si>
-    <t>-8991</t>
-  </si>
-  <si>
-    <t>-258</t>
-  </si>
-  <si>
-    <t>-216</t>
-  </si>
-  <si>
-    <t>+109</t>
-  </si>
-  <si>
-    <t>+1289</t>
-  </si>
-  <si>
-    <t>+3233</t>
-  </si>
-  <si>
-    <t>+3900</t>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>97.4%</t>
+  </si>
+  <si>
+    <t>85.8%</t>
+  </si>
+  <si>
+    <t>76.1%</t>
+  </si>
+  <si>
+    <t>75.6%</t>
+  </si>
+  <si>
+    <t>54.0%</t>
+  </si>
+  <si>
+    <t>6.8%</t>
+  </si>
+  <si>
+    <t>2.1%</t>
+  </si>
+  <si>
+    <t>1.9%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>-3746</t>
+  </si>
+  <si>
+    <t>-604</t>
+  </si>
+  <si>
+    <t>-318</t>
+  </si>
+  <si>
+    <t>-310</t>
+  </si>
+  <si>
+    <t>-117</t>
+  </si>
+  <si>
+    <t>+1371</t>
+  </si>
+  <si>
+    <t>+4662</t>
+  </si>
+  <si>
+    <t>+5163</t>
+  </si>
+  <si>
+    <t>+33233</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>58.1%</t>
+  </si>
+  <si>
+    <t>18.1%</t>
+  </si>
+  <si>
+    <t>10.6%</t>
+  </si>
+  <si>
+    <t>9.4%</t>
+  </si>
+  <si>
+    <t>3.8%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-139</t>
+  </si>
+  <si>
+    <t>+452</t>
+  </si>
+  <si>
+    <t>+843</t>
+  </si>
+  <si>
+    <t>+964</t>
+  </si>
+  <si>
+    <t>+2532</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>55.5%</t>
-  </si>
-  <si>
-    <t>39.8%</t>
-  </si>
-  <si>
-    <t>2.1%</t>
-  </si>
-  <si>
-    <t>1.8%</t>
-  </si>
-  <si>
-    <t>0.8%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-125</t>
-  </si>
-  <si>
-    <t>+151</t>
-  </si>
-  <si>
-    <t>+4662</t>
-  </si>
-  <si>
-    <t>+5456</t>
-  </si>
-  <si>
-    <t>+12400</t>
-  </si>
-  <si>
-    <t>59.3%</t>
-  </si>
-  <si>
-    <t>17.8%</t>
-  </si>
-  <si>
-    <t>17.1%</t>
-  </si>
-  <si>
-    <t>5.5%</t>
-  </si>
-  <si>
-    <t>-146</t>
-  </si>
-  <si>
-    <t>+462</t>
-  </si>
-  <si>
-    <t>+485</t>
-  </si>
-  <si>
-    <t>+1718</t>
+    <t>63.1%</t>
+  </si>
+  <si>
+    <t>17.0%</t>
+  </si>
+  <si>
+    <t>13.4%</t>
+  </si>
+  <si>
+    <t>6.5%</t>
+  </si>
+  <si>
+    <t>-171</t>
+  </si>
+  <si>
+    <t>+488</t>
+  </si>
+  <si>
+    <t>+646</t>
+  </si>
+  <si>
+    <t>+1438</t>
   </si>
 </sst>
 </file>
@@ -577,7 +580,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
@@ -619,7 +622,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
@@ -633,7 +636,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
@@ -727,7 +730,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>38</v>
@@ -769,7 +772,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
         <v>41</v>
@@ -789,26 +792,26 @@
         <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
@@ -817,12 +820,12 @@
         <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
@@ -831,7 +834,7 @@
         <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -866,10 +869,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -880,10 +883,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -894,10 +897,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -905,60 +908,60 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -967,21 +970,21 @@
         <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
         <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Ketkar Fantasy Football 2026 2026 Betting Odds.xlsx
+++ b/data/odds/Ketkar Fantasy Football 2026 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="60">
   <si>
     <t>Record</t>
   </si>
@@ -30,163 +30,172 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Walnut Rushers</t>
+  </si>
+  <si>
     <t>Dillan</t>
   </si>
   <si>
+    <t xml:space="preserve">Ashu’s Seahawks </t>
+  </si>
+  <si>
     <t>Austin Powers</t>
   </si>
   <si>
     <t>Sharrell’s Peril</t>
   </si>
   <si>
-    <t>Walnut Rushers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashu’s Seahawks </t>
+    <t>FP Jets</t>
   </si>
   <si>
     <t xml:space="preserve">Gotham City Gridiron Gang </t>
   </si>
   <si>
-    <t>FP Jets</t>
+    <t>Akshata's Angry Team</t>
   </si>
   <si>
     <t>Lox, Stocks and 2 Skattebooms!</t>
   </si>
   <si>
-    <t>Akshata's Angry Team</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>4-2</t>
   </si>
   <si>
     <t>3-2</t>
   </si>
   <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>97.4%</t>
-  </si>
-  <si>
-    <t>85.8%</t>
-  </si>
-  <si>
-    <t>76.1%</t>
-  </si>
-  <si>
-    <t>75.6%</t>
-  </si>
-  <si>
-    <t>54.0%</t>
-  </si>
-  <si>
-    <t>6.8%</t>
-  </si>
-  <si>
-    <t>2.1%</t>
-  </si>
-  <si>
-    <t>1.9%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>-3746</t>
-  </si>
-  <si>
-    <t>-604</t>
-  </si>
-  <si>
-    <t>-318</t>
-  </si>
-  <si>
-    <t>-310</t>
-  </si>
-  <si>
-    <t>-117</t>
-  </si>
-  <si>
-    <t>+1371</t>
-  </si>
-  <si>
-    <t>+4662</t>
-  </si>
-  <si>
-    <t>+5163</t>
-  </si>
-  <si>
-    <t>+33233</t>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>94.9%</t>
+  </si>
+  <si>
+    <t>92.8%</t>
+  </si>
+  <si>
+    <t>77.1%</t>
+  </si>
+  <si>
+    <t>74.5%</t>
+  </si>
+  <si>
+    <t>49.6%</t>
+  </si>
+  <si>
+    <t>5.4%</t>
+  </si>
+  <si>
+    <t>4.2%</t>
+  </si>
+  <si>
+    <t>0.8%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>-1861</t>
+  </si>
+  <si>
+    <t>-1289</t>
+  </si>
+  <si>
+    <t>-337</t>
+  </si>
+  <si>
+    <t>-292</t>
+  </si>
+  <si>
+    <t>+102</t>
+  </si>
+  <si>
+    <t>+1752</t>
+  </si>
+  <si>
+    <t>+2281</t>
+  </si>
+  <si>
+    <t>+12400</t>
+  </si>
+  <si>
+    <t>+14186</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>58.1%</t>
-  </si>
-  <si>
-    <t>18.1%</t>
-  </si>
-  <si>
-    <t>10.6%</t>
-  </si>
-  <si>
-    <t>9.4%</t>
-  </si>
-  <si>
-    <t>3.8%</t>
+    <t>43.4%</t>
+  </si>
+  <si>
+    <t>34.1%</t>
+  </si>
+  <si>
+    <t>9.6%</t>
+  </si>
+  <si>
+    <t>8.5%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-139</t>
-  </si>
-  <si>
-    <t>+452</t>
-  </si>
-  <si>
-    <t>+843</t>
-  </si>
-  <si>
-    <t>+964</t>
-  </si>
-  <si>
-    <t>+2532</t>
+    <t>+130</t>
+  </si>
+  <si>
+    <t>+193</t>
+  </si>
+  <si>
+    <t>+942</t>
+  </si>
+  <si>
+    <t>+1076</t>
+  </si>
+  <si>
+    <t>+49900</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>63.1%</t>
-  </si>
-  <si>
-    <t>17.0%</t>
-  </si>
-  <si>
-    <t>13.4%</t>
-  </si>
-  <si>
-    <t>6.5%</t>
-  </si>
-  <si>
-    <t>-171</t>
-  </si>
-  <si>
-    <t>+488</t>
-  </si>
-  <si>
-    <t>+646</t>
-  </si>
-  <si>
-    <t>+1438</t>
+    <t>39.7%</t>
+  </si>
+  <si>
+    <t>38.5%</t>
+  </si>
+  <si>
+    <t>12.2%</t>
+  </si>
+  <si>
+    <t>9.0%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>+152</t>
+  </si>
+  <si>
+    <t>+160</t>
+  </si>
+  <si>
+    <t>+720</t>
+  </si>
+  <si>
+    <t>+1011</t>
+  </si>
+  <si>
+    <t>+16567</t>
   </si>
 </sst>
 </file>
@@ -569,10 +578,10 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -583,10 +592,10 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -594,13 +603,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -608,13 +617,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -622,13 +631,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -636,13 +645,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -650,13 +659,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -667,10 +676,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -678,13 +687,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -719,10 +728,10 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -733,10 +742,10 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -744,13 +753,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -758,13 +767,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -772,18 +781,18 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
@@ -797,44 +806,44 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -855,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -863,30 +872,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -894,13 +903,13 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -908,83 +917,83 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Ketkar Fantasy Football 2026 2026 Betting Odds.xlsx
+++ b/data/odds/Ketkar Fantasy Football 2026 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="63">
   <si>
     <t>Record</t>
   </si>
@@ -36,15 +36,15 @@
     <t>Dillan</t>
   </si>
   <si>
+    <t>Sharrell’s Peril</t>
+  </si>
+  <si>
+    <t>Austin Powers</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ashu’s Seahawks </t>
   </si>
   <si>
-    <t>Austin Powers</t>
-  </si>
-  <si>
-    <t>Sharrell’s Peril</t>
-  </si>
-  <si>
     <t>FP Jets</t>
   </si>
   <si>
@@ -57,145 +57,154 @@
     <t>Lox, Stocks and 2 Skattebooms!</t>
   </si>
   <si>
-    <t>4-1</t>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>4-2</t>
   </si>
   <si>
     <t>3-3</t>
   </si>
   <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>94.9%</t>
-  </si>
-  <si>
-    <t>92.8%</t>
-  </si>
-  <si>
-    <t>77.1%</t>
-  </si>
-  <si>
-    <t>74.5%</t>
-  </si>
-  <si>
-    <t>49.6%</t>
-  </si>
-  <si>
-    <t>5.4%</t>
-  </si>
-  <si>
-    <t>4.2%</t>
-  </si>
-  <si>
-    <t>0.8%</t>
-  </si>
-  <si>
-    <t>0.7%</t>
-  </si>
-  <si>
-    <t>-1861</t>
-  </si>
-  <si>
-    <t>-1289</t>
-  </si>
-  <si>
-    <t>-337</t>
-  </si>
-  <si>
-    <t>-292</t>
-  </si>
-  <si>
-    <t>+102</t>
-  </si>
-  <si>
-    <t>+1752</t>
-  </si>
-  <si>
-    <t>+2281</t>
-  </si>
-  <si>
-    <t>+12400</t>
-  </si>
-  <si>
-    <t>+14186</t>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>1-6</t>
+  </si>
+  <si>
+    <t>99.6%</t>
+  </si>
+  <si>
+    <t>98.1%</t>
+  </si>
+  <si>
+    <t>83.3%</t>
+  </si>
+  <si>
+    <t>66.9%</t>
+  </si>
+  <si>
+    <t>26.7%</t>
+  </si>
+  <si>
+    <t>17.0%</t>
+  </si>
+  <si>
+    <t>4.6%</t>
+  </si>
+  <si>
+    <t>3.3%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>-24900</t>
+  </si>
+  <si>
+    <t>-5163</t>
+  </si>
+  <si>
+    <t>-499</t>
+  </si>
+  <si>
+    <t>-202</t>
+  </si>
+  <si>
+    <t>+275</t>
+  </si>
+  <si>
+    <t>+488</t>
+  </si>
+  <si>
+    <t>+2074</t>
+  </si>
+  <si>
+    <t>+2930</t>
+  </si>
+  <si>
+    <t>+19900</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>43.4%</t>
-  </si>
-  <si>
-    <t>34.1%</t>
-  </si>
-  <si>
-    <t>9.6%</t>
-  </si>
-  <si>
-    <t>8.5%</t>
+    <t>59.1%</t>
+  </si>
+  <si>
+    <t>32.2%</t>
+  </si>
+  <si>
+    <t>7.0%</t>
+  </si>
+  <si>
+    <t>1.0%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-144</t>
+  </si>
+  <si>
+    <t>+211</t>
+  </si>
+  <si>
+    <t>+1329</t>
+  </si>
+  <si>
+    <t>+9900</t>
+  </si>
+  <si>
+    <t>+16567</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>51.8%</t>
+  </si>
+  <si>
+    <t>25.6%</t>
+  </si>
+  <si>
+    <t>14.8%</t>
+  </si>
+  <si>
+    <t>4.7%</t>
+  </si>
+  <si>
+    <t>2.8%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>+130</t>
-  </si>
-  <si>
-    <t>+193</t>
-  </si>
-  <si>
-    <t>+942</t>
-  </si>
-  <si>
-    <t>+1076</t>
+    <t>-107</t>
+  </si>
+  <si>
+    <t>+291</t>
+  </si>
+  <si>
+    <t>+576</t>
+  </si>
+  <si>
+    <t>+2028</t>
+  </si>
+  <si>
+    <t>+3471</t>
   </si>
   <si>
     <t>+49900</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>39.7%</t>
-  </si>
-  <si>
-    <t>38.5%</t>
-  </si>
-  <si>
-    <t>12.2%</t>
-  </si>
-  <si>
-    <t>9.0%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>+152</t>
-  </si>
-  <si>
-    <t>+160</t>
-  </si>
-  <si>
-    <t>+720</t>
-  </si>
-  <si>
-    <t>+1011</t>
-  </si>
-  <si>
-    <t>+16567</t>
   </si>
 </sst>
 </file>
@@ -631,7 +640,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
@@ -645,7 +654,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
         <v>24</v>
@@ -731,7 +740,7 @@
         <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -745,7 +754,7 @@
         <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -759,7 +768,7 @@
         <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -773,7 +782,7 @@
         <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -781,27 +790,27 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -812,24 +821,24 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -840,10 +849,10 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -872,30 +881,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -906,66 +915,66 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -976,10 +985,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -990,10 +999,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Ketkar Fantasy Football 2026 2026 Betting Odds.xlsx
+++ b/data/odds/Ketkar Fantasy Football 2026 2026 Betting Odds.xlsx
@@ -75,55 +75,55 @@
     <t>1-6</t>
   </si>
   <si>
-    <t>99.6%</t>
-  </si>
-  <si>
-    <t>98.1%</t>
-  </si>
-  <si>
-    <t>83.3%</t>
-  </si>
-  <si>
-    <t>66.9%</t>
-  </si>
-  <si>
-    <t>26.7%</t>
-  </si>
-  <si>
-    <t>17.0%</t>
-  </si>
-  <si>
-    <t>4.6%</t>
-  </si>
-  <si>
-    <t>3.3%</t>
+    <t>99.1%</t>
+  </si>
+  <si>
+    <t>97.9%</t>
+  </si>
+  <si>
+    <t>84.7%</t>
+  </si>
+  <si>
+    <t>65.7%</t>
+  </si>
+  <si>
+    <t>26.0%</t>
+  </si>
+  <si>
+    <t>17.8%</t>
+  </si>
+  <si>
+    <t>5.1%</t>
+  </si>
+  <si>
+    <t>3.2%</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>-24900</t>
-  </si>
-  <si>
-    <t>-5163</t>
-  </si>
-  <si>
-    <t>-499</t>
-  </si>
-  <si>
-    <t>-202</t>
-  </si>
-  <si>
-    <t>+275</t>
-  </si>
-  <si>
-    <t>+488</t>
-  </si>
-  <si>
-    <t>+2074</t>
-  </si>
-  <si>
-    <t>+2930</t>
+    <t>-11011</t>
+  </si>
+  <si>
+    <t>-4662</t>
+  </si>
+  <si>
+    <t>-554</t>
+  </si>
+  <si>
+    <t>-192</t>
+  </si>
+  <si>
+    <t>+285</t>
+  </si>
+  <si>
+    <t>+462</t>
+  </si>
+  <si>
+    <t>+1861</t>
+  </si>
+  <si>
+    <t>+3025</t>
   </si>
   <si>
     <t>+19900</t>
@@ -132,19 +132,16 @@
     <t>Probability</t>
   </si>
   <si>
-    <t>59.1%</t>
-  </si>
-  <si>
-    <t>32.2%</t>
-  </si>
-  <si>
-    <t>7.0%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
+    <t>57.5%</t>
+  </si>
+  <si>
+    <t>34.4%</t>
+  </si>
+  <si>
+    <t>6.3%</t>
+  </si>
+  <si>
+    <t>1.2%</t>
   </si>
   <si>
     <t>0.1%</t>
@@ -153,55 +150,58 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>-144</t>
-  </si>
-  <si>
-    <t>+211</t>
-  </si>
-  <si>
-    <t>+1329</t>
-  </si>
-  <si>
-    <t>+9900</t>
-  </si>
-  <si>
-    <t>+16567</t>
+    <t>-135</t>
+  </si>
+  <si>
+    <t>+191</t>
+  </si>
+  <si>
+    <t>+1487</t>
+  </si>
+  <si>
+    <t>+8233</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>51.8%</t>
-  </si>
-  <si>
-    <t>25.6%</t>
-  </si>
-  <si>
-    <t>14.8%</t>
+    <t>48.6%</t>
+  </si>
+  <si>
+    <t>24.3%</t>
+  </si>
+  <si>
+    <t>19.1%</t>
   </si>
   <si>
     <t>4.7%</t>
   </si>
   <si>
-    <t>2.8%</t>
+    <t>2.7%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>-107</t>
-  </si>
-  <si>
-    <t>+291</t>
-  </si>
-  <si>
-    <t>+576</t>
+    <t>+106</t>
+  </si>
+  <si>
+    <t>+312</t>
+  </si>
+  <si>
+    <t>+424</t>
   </si>
   <si>
     <t>+2028</t>
   </si>
   <si>
-    <t>+3471</t>
+    <t>+3604</t>
+  </si>
+  <si>
+    <t>+24900</t>
   </si>
   <si>
     <t>+49900</t>
@@ -740,7 +740,7 @@
         <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -754,7 +754,7 @@
         <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -768,7 +768,7 @@
         <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -782,7 +782,7 @@
         <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -793,10 +793,10 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -807,10 +807,10 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -821,10 +821,10 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -835,10 +835,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -849,10 +849,10 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -887,10 +887,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -901,10 +901,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -915,10 +915,10 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -929,10 +929,10 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -943,10 +943,10 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -957,10 +957,10 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -971,10 +971,10 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -985,10 +985,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -999,10 +999,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
